--- a/config/excel/CfgRogueRewards.xlsx
+++ b/config/excel/CfgRogueRewards.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRogueRewards" sheetId="1" r:id="R642500b8071a4e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgRogueRewards" sheetId="1" r:id="R5115631ed64e45fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="200" formatCode="@"/>
+    <x:numFmt numFmtId="201" formatCode="General"/>
+  </x:numFmts>
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -33,8 +37,19 @@
       <x:color rgb="FF0000FF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -56,6 +71,21 @@
         <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDCE6F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -63,7 +93,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -90,6 +120,28 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -294,377 +346,828 @@
   <x:cols>
     <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="36" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="65" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="24" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="24" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="10" t="str">
         <x:v>ID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>Title</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>Description</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>Kind</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>Amount</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>LootType</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>Weight</x:v>
       </x:c>
+      <x:c r="I1" s="12" t="str">
+        <x:v>AugmentID</x:v>
+      </x:c>
+      <x:c r="J1" s="12" t="str">
+        <x:v>MaxRank</x:v>
+      </x:c>
+      <x:c r="K1" s="12" t="str">
+        <x:v>PrerequisiteID</x:v>
+      </x:c>
+      <x:c r="L1" s="12" t="str">
+        <x:v>PrerequisiteRank</x:v>
+      </x:c>
+      <x:c r="M1" s="12" t="str">
+        <x:v>ExclusiveGroup</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="6" t="str">
+      <x:c r="A2" s="13" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="B2" s="6" t="str">
+      <x:c r="B2" s="13" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="C2" s="13" t="str">
         <x:v>string</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
+      <x:c r="D2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
+      <x:c r="E2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="str">
+      <x:c r="F2" s="13" t="str">
         <x:v>number</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="str">
+      <x:c r="G2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="6" t="str">
+      <x:c r="H2" s="13" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>string</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="42" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+      <x:c r="A3" s="15" t="str">
         <x:v># 奖励稳定身份</x:v>
       </x:c>
-      <x:c r="B3" s="8" t="str">
+      <x:c r="B3" s="15" t="str">
         <x:v>奖励名称</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="15" t="str">
         <x:v>奖励说明</x:v>
       </x:c>
-      <x:c r="D3" s="8" t="str">
+      <x:c r="D3" s="15" t="str">
         <x:v>奖励类型枚举值</x:v>
       </x:c>
-      <x:c r="E3" s="8" t="str">
+      <x:c r="E3" s="15" t="str">
         <x:v>属性枚举值</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="15" t="str">
         <x:v>属性增加量</x:v>
       </x:c>
-      <x:c r="G3" s="8" t="str">
+      <x:c r="G3" s="15" t="str">
         <x:v>随机物品类型枚举值</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str">
+      <x:c r="H3" s="15" t="str">
         <x:v>抽取权重</x:v>
       </x:c>
+      <x:c r="I3" s="16" t="str">
+        <x:v>战斗强化定义，非战斗奖励留空</x:v>
+      </x:c>
+      <x:c r="J3" s="16" t="str">
+        <x:v>最高等级；0为不限</x:v>
+      </x:c>
+      <x:c r="K3" s="16" t="str">
+        <x:v>前置奖励ID，空为无</x:v>
+      </x:c>
+      <x:c r="L3" s="16" t="str">
+        <x:v>前置最低等级</x:v>
+      </x:c>
+      <x:c r="M3" s="16" t="str">
+        <x:v>互斥组，空为无</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
-      <x:c r="A4" s="9" t="str">
+      <x:c r="A4" s="17" t="str">
         <x:v>hp</x:v>
       </x:c>
-      <x:c r="B4" s="9" t="str">
+      <x:c r="B4" s="17" t="str">
         <x:v>生命强化</x:v>
       </x:c>
-      <x:c r="C4" s="9" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>本局生命上限和当前生命均 +20</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="n">
+      <x:c r="D4" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G4" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="19" t="str"/>
+      <x:c r="J4" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K4" s="19" t="str"/>
+      <x:c r="L4" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" s="19" t="str"/>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
-      <x:c r="A5" s="9" t="str">
+      <x:c r="A5" s="17" t="str">
         <x:v>attack</x:v>
       </x:c>
-      <x:c r="B5" s="9" t="str">
+      <x:c r="B5" s="17" t="str">
         <x:v>攻击强化</x:v>
       </x:c>
-      <x:c r="C5" s="9" t="str">
+      <x:c r="C5" s="17" t="str">
         <x:v>本局攻击 +4</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="n">
+      <x:c r="D5" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G5" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I5" s="19" t="str"/>
+      <x:c r="J5" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="19" t="str"/>
+      <x:c r="L5" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="19" t="str"/>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="9" t="str">
+      <x:c r="A6" s="17" t="str">
         <x:v>defense</x:v>
       </x:c>
-      <x:c r="B6" s="9" t="str">
+      <x:c r="B6" s="17" t="str">
         <x:v>防御强化</x:v>
       </x:c>
-      <x:c r="C6" s="9" t="str">
+      <x:c r="C6" s="17" t="str">
         <x:v>本局防御 +8</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="3" t="n">
+      <x:c r="D6" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="n">
+      <x:c r="F6" s="20" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G6" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="19" t="str"/>
+      <x:c r="J6" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="19" t="str"/>
+      <x:c r="L6" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" s="19" t="str"/>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="9" t="str">
+      <x:c r="A7" s="17" t="str">
         <x:v>critical</x:v>
       </x:c>
-      <x:c r="B7" s="9" t="str">
+      <x:c r="B7" s="17" t="str">
         <x:v>暴击强化</x:v>
       </x:c>
-      <x:c r="C7" s="9" t="str">
+      <x:c r="C7" s="17" t="str">
         <x:v>本局暴击值 +12</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F7" s="3" t="n">
+      <x:c r="D7" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G7" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I7" s="19" t="str"/>
+      <x:c r="J7" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="19" t="str"/>
+      <x:c r="L7" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M7" s="19" t="str"/>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="9" t="str">
+      <x:c r="A8" s="17" t="str">
         <x:v>critical_damage</x:v>
       </x:c>
-      <x:c r="B8" s="9" t="str">
+      <x:c r="B8" s="17" t="str">
         <x:v>暴伤强化</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="str">
+      <x:c r="C8" s="17" t="str">
         <x:v>本局暴击伤害 +20 个百分点</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="3" t="n">
+      <x:c r="D8" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="n">
+      <x:c r="F8" s="20" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G8" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="19" t="str"/>
+      <x:c r="J8" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="19" t="str"/>
+      <x:c r="L8" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" s="19" t="str"/>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="9" t="str">
+      <x:c r="A9" s="17" t="str">
         <x:v>dodge</x:v>
       </x:c>
-      <x:c r="B9" s="9" t="str">
+      <x:c r="B9" s="17" t="str">
         <x:v>闪避强化</x:v>
       </x:c>
-      <x:c r="C9" s="9" t="str">
+      <x:c r="C9" s="17" t="str">
         <x:v>本局闪避率 +5%</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="3" t="n">
+      <x:c r="D9" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="n">
+      <x:c r="F9" s="20" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G9" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="19" t="str"/>
+      <x:c r="J9" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="19" t="str"/>
+      <x:c r="L9" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" s="19" t="str"/>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="9" t="str">
+      <x:c r="A10" s="17" t="str">
         <x:v>increase</x:v>
       </x:c>
-      <x:c r="B10" s="9" t="str">
+      <x:c r="B10" s="17" t="str">
         <x:v>增伤强化</x:v>
       </x:c>
-      <x:c r="C10" s="9" t="str">
+      <x:c r="C10" s="17" t="str">
         <x:v>本局增伤 +10%</x:v>
       </x:c>
-      <x:c r="D10" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" s="3" t="n">
+      <x:c r="D10" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="20" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="n">
+      <x:c r="F10" s="20" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H10" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G10" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="19" t="str"/>
+      <x:c r="J10" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="19" t="str"/>
+      <x:c r="L10" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" s="19" t="str"/>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="9" t="str">
+      <x:c r="A11" s="17" t="str">
         <x:v>reduction</x:v>
       </x:c>
-      <x:c r="B11" s="9" t="str">
+      <x:c r="B11" s="17" t="str">
         <x:v>减伤强化</x:v>
       </x:c>
-      <x:c r="C11" s="9" t="str">
+      <x:c r="C11" s="17" t="str">
         <x:v>本局减伤 +5%</x:v>
       </x:c>
-      <x:c r="D11" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="3" t="n">
+      <x:c r="D11" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="20" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="n">
+      <x:c r="F11" s="20" t="n">
         <x:v>0.05</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="G11" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I11" s="19" t="str"/>
+      <x:c r="J11" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="19" t="str"/>
+      <x:c r="L11" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="19" t="str"/>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
-      <x:c r="A12" s="9" t="str">
+      <x:c r="A12" s="17" t="str">
         <x:v>weapon</x:v>
       </x:c>
-      <x:c r="B12" s="9" t="str">
+      <x:c r="B12" s="17" t="str">
         <x:v>随机武器</x:v>
       </x:c>
-      <x:c r="C12" s="9" t="str">
+      <x:c r="C12" s="17" t="str">
         <x:v>本局获得随机武器</x:v>
       </x:c>
-      <x:c r="D12" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D12" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I12" s="19" t="str"/>
+      <x:c r="J12" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="19" t="str"/>
+      <x:c r="L12" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" s="19" t="str"/>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="9" t="str">
+      <x:c r="A13" s="17" t="str">
         <x:v>armor</x:v>
       </x:c>
-      <x:c r="B13" s="9" t="str">
+      <x:c r="B13" s="17" t="str">
         <x:v>随机护甲</x:v>
       </x:c>
-      <x:c r="C13" s="9" t="str">
+      <x:c r="C13" s="17" t="str">
         <x:v>本局获得随机护甲</x:v>
       </x:c>
-      <x:c r="D13" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="3" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H13" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="D13" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E13" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H13" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I13" s="19" t="str"/>
+      <x:c r="J13" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="19" t="str"/>
+      <x:c r="L13" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="19" t="str"/>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="9" t="str">
+      <x:c r="A14" s="17" t="str">
         <x:v>item</x:v>
       </x:c>
-      <x:c r="B14" s="9" t="str">
+      <x:c r="B14" s="17" t="str">
         <x:v>随机物品</x:v>
       </x:c>
-      <x:c r="C14" s="9" t="str">
+      <x:c r="C14" s="17" t="str">
         <x:v>本局获得随机物品</x:v>
       </x:c>
-      <x:c r="D14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F14" s="3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="3" t="n">
+      <x:c r="D14" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E14" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="20" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="H14" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="19" t="str"/>
+      <x:c r="J14" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="19" t="str"/>
+      <x:c r="L14" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" s="19" t="str"/>
+    </x:row>
+    <x:row r="15" ht="52" customHeight="1">
+      <x:c r="A15" s="19" t="str">
+        <x:v>bleed</x:v>
+      </x:c>
+      <x:c r="B15" s="19" t="str">
+        <x:v>割裂</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="str">
+        <x:v>每级增加20%命中施加流血概率；持续3秒、每秒每层3伤害，最多3层。</x:v>
+      </x:c>
+      <x:c r="D15" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E15" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="21" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="G15" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I15" s="19" t="str">
+        <x:v>bleed</x:v>
+      </x:c>
+      <x:c r="J15" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K15" s="19" t="str"/>
+      <x:c r="L15" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" s="19" t="str"/>
+    </x:row>
+    <x:row r="16" ht="52" customHeight="1">
+      <x:c r="A16" s="19" t="str">
+        <x:v>critical_echo</x:v>
+      </x:c>
+      <x:c r="B16" s="19" t="str">
+        <x:v>暴击追伤</x:v>
+      </x:c>
+      <x:c r="C16" s="19" t="str">
+        <x:v>每级在暴击时追加40%攻击力伤害；每0.75秒最多触发一次。</x:v>
+      </x:c>
+      <x:c r="D16" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E16" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G16" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I16" s="19" t="str">
+        <x:v>critical_echo</x:v>
+      </x:c>
+      <x:c r="J16" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K16" s="19" t="str"/>
+      <x:c r="L16" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" s="19" t="str"/>
+    </x:row>
+    <x:row r="17" ht="52" customHeight="1">
+      <x:c r="A17" s="19" t="str">
+        <x:v>kill_leech</x:v>
+      </x:c>
+      <x:c r="B17" s="19" t="str">
+        <x:v>猎杀回复</x:v>
+      </x:c>
+      <x:c r="C17" s="19" t="str">
+        <x:v>每级在击杀时回复4点生命；衍生伤害不再次触发被动。</x:v>
+      </x:c>
+      <x:c r="D17" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G17" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I17" s="19" t="str">
+        <x:v>kill_leech</x:v>
+      </x:c>
+      <x:c r="J17" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K17" s="19" t="str"/>
+      <x:c r="L17" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="19" t="str"/>
+    </x:row>
+    <x:row r="18" ht="52" customHeight="1">
+      <x:c r="A18" s="19" t="str">
+        <x:v>retaliation</x:v>
+      </x:c>
+      <x:c r="B18" s="19" t="str">
+        <x:v>荆棘反击</x:v>
+      </x:c>
+      <x:c r="C18" s="19" t="str">
+        <x:v>每级受伤时向伤害来源反击30%攻击力伤害；间隔1.5秒。</x:v>
+      </x:c>
+      <x:c r="D18" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G18" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I18" s="19" t="str">
+        <x:v>retaliation</x:v>
+      </x:c>
+      <x:c r="J18" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K18" s="19" t="str"/>
+      <x:c r="L18" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" s="19" t="str"/>
+    </x:row>
+    <x:row r="19" ht="52" customHeight="1">
+      <x:c r="A19" s="19" t="str">
+        <x:v>swift_blade</x:v>
+      </x:c>
+      <x:c r="B19" s="19" t="str">
+        <x:v>疾风架势</x:v>
+      </x:c>
+      <x:c r="C19" s="19" t="str">
+        <x:v>每级缩短基础攻击冷却8%；冷却不会短于攻击动作。与重击架势互斥。</x:v>
+      </x:c>
+      <x:c r="D19" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="21" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="G19" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I19" s="19" t="str">
+        <x:v>swift_blade</x:v>
+      </x:c>
+      <x:c r="J19" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K19" s="19" t="str"/>
+      <x:c r="L19" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" s="19" t="str">
+        <x:v>stance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="52" customHeight="1">
+      <x:c r="A20" s="19" t="str">
+        <x:v>wide_blade</x:v>
+      </x:c>
+      <x:c r="B20" s="19" t="str">
+        <x:v>横扫强化</x:v>
+      </x:c>
+      <x:c r="C20" s="19" t="str">
+        <x:v>每级扩大基础攻击范围15%。</x:v>
+      </x:c>
+      <x:c r="D20" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E20" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="21" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="G20" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I20" s="19" t="str">
+        <x:v>wide_blade</x:v>
+      </x:c>
+      <x:c r="J20" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K20" s="19" t="str"/>
+      <x:c r="L20" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" s="19" t="str"/>
+    </x:row>
+    <x:row r="21" ht="52" customHeight="1">
+      <x:c r="A21" s="19" t="str">
+        <x:v>heavy_blade</x:v>
+      </x:c>
+      <x:c r="B21" s="19" t="str">
+        <x:v>重击架势</x:v>
+      </x:c>
+      <x:c r="C21" s="19" t="str">
+        <x:v>每级提高基础攻击伤害15%。与疾风架势互斥。</x:v>
+      </x:c>
+      <x:c r="D21" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E21" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="21" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="G21" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I21" s="19" t="str">
+        <x:v>heavy_blade</x:v>
+      </x:c>
+      <x:c r="J21" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K21" s="19" t="str"/>
+      <x:c r="L21" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" s="19" t="str">
+        <x:v>stance</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="52" customHeight="1">
+      <x:c r="A22" s="19" t="str">
+        <x:v>bloodlust</x:v>
+      </x:c>
+      <x:c r="B22" s="19" t="str">
+        <x:v>嗜血追猎</x:v>
+      </x:c>
+      <x:c r="C22" s="19" t="str">
+        <x:v>割裂达到2级后解锁；击杀额外回复8点生命。</x:v>
+      </x:c>
+      <x:c r="D22" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E22" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G22" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I22" s="19" t="str">
+        <x:v>kill_leech</x:v>
+      </x:c>
+      <x:c r="J22" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K22" s="19" t="str">
+        <x:v>bleed</x:v>
+      </x:c>
+      <x:c r="L22" s="21" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M22" s="19" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
